--- a/03_Outputs/Turistica_Agroecologica/09_Salud/salud.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/09_Salud/salud.xlsx
@@ -742,7 +742,7 @@
     <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
     <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
     <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -778,7 +778,7 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Tasa de leishmaniasis por 100 mil hab.</t>
+          <t>Tasa de leishmaniasis por 100 mil hab. rurales</t>
         </is>
       </c>
     </row>

--- a/03_Outputs/Turistica_Agroecologica/09_Salud/salud.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/09_Salud/salud.xlsx
@@ -1013,7 +1013,7 @@
         <v>3.04173441288142</v>
       </c>
       <c r="G9" s="11">
-        <v>60.0929957814647</v>
+        <v>60.0929957814648</v>
       </c>
     </row>
   </sheetData>
